--- a/BBS_converted_dia16.xlsx
+++ b/BBS_converted_dia16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZAZ\Desktop\Buniyadbyte_codes\Codes\Buniyadbyte\BB_waste\POC_waste\Contnous_beam_poc\poc-waste-proper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD33288B-6539-4D58-AB44-72962DB1C5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73F91EE-8E32-4BCF-BDEF-6662D32EBB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1595</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
